--- a/docs/test-cases/SPM-54_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-54_Test_Cases.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -67,6 +67,9 @@
       <name val="Arial"/>
       <color rgb="FF000000"/>
       <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -163,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -231,6 +234,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -523,12 +529,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>SPM-54: As the assigned Event Coordinator, I want to move an approved event into planning so that venue, equipment and other arrangements can begin</t>
         </is>
@@ -540,32 +546,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -592,27 +598,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC01</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pressing Search on Find a venue for an Approved event moves it to Planning</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -631,27 +637,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC02</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Organiser sees that their event has entered Planning</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -670,27 +676,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC03</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Organiser of an event that has not begun planning still sees Approved</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -709,27 +715,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC04</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Requesting a venue booking for an Approved event moves it to Planning</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -752,27 +758,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC05</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Recording equipment for an Approved event moves it to Planning</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -791,27 +797,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC06</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Saving a change to an equipment item on an Approved event moves it to Planning</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -830,27 +836,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC07</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Removing an equipment item from an Approved event moves it to Planning</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -869,38 +875,42 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC08</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>A venue search by anyone other than the assigned coordinator does not begin planning</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -908,27 +918,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC09</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Opening the pages, 'Clear filters' and 'Cancel' do not begin planning</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -947,27 +957,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC10</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Cancelling the 'Begin planning?' dialog leaves the event Approved and does not carry out the action</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -986,27 +996,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC11</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>A venue search leaves an Under review event and an event already in Planning unchanged</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1025,27 +1035,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC12</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Before approval, a venue booking cannot be requested and equipment cannot be recorded</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1064,27 +1074,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC13</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>A venue search does not pull a Confirmed or Rejected event into Planning</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1103,27 +1113,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC14</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Once in Planning, the coordinator can request a venue booking and record equipment, and sees each with its status</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1141,20 +1151,21 @@
       </c>
     </row>
     <row r="18"/>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
       <c r="D20" s="27" t="n"/>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1162,19 +1173,19 @@
       <c r="F20" s="27" t="n"/>
     </row>
     <row r="21" ht="111.75" customHeight="1" s="25">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Given an event has been Approved, when the assigned Coordinator begins planning, then the event status changes to Planning.</t>
         </is>
       </c>
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="27" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC01
 SPM-54-TC04
@@ -1189,19 +1200,19 @@
       <c r="F21" s="27" t="n"/>
     </row>
     <row r="22" ht="57.75" customHeight="1" s="25">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>An event can only move to Planning from an Approved status.</t>
         </is>
       </c>
       <c r="C22" s="26" t="n"/>
       <c r="D22" s="27" t="n"/>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC01
 SPM-54-TC11
@@ -1212,19 +1223,19 @@
       <c r="F22" s="27" t="n"/>
     </row>
     <row r="23" ht="84.75" customHeight="1" s="25">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Once in Planning, the Coordinator can proceed to request venue bookings, record equipment requirements, and track outstanding arrangements.</t>
         </is>
       </c>
       <c r="C23" s="26" t="n"/>
       <c r="D23" s="27" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC04
 SPM-54-TC05
@@ -1237,19 +1248,19 @@
       <c r="F23" s="27" t="n"/>
     </row>
     <row r="24" ht="30.75" customHeight="1" s="25">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>The Event Organiser can view that their event has entered planning.</t>
         </is>
       </c>
       <c r="C24" s="26" t="n"/>
       <c r="D24" s="27" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC02
 SPM-54-TC03</t>
@@ -1259,12 +1270,12 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="354.75" customHeight="1" s="25">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>docs/PERMISSIONS.md
 docs/test-cases/SPM-40_test_cases.json
@@ -2315,7 +2326,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -2323,33 +2334,40 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-54-TC08</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="152.25" customHeight="1" s="25">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-54-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="341.25" customHeight="1" s="25">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Logged out.
@@ -2358,13 +2376,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="341.25" customHeight="1" s="25">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Log in as Priya Raj
  2. Click 'All Events' in the sidebar and open 'SPM54 Meridian Budget Briefing'
@@ -2389,25 +2407,25 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Event: SPM54 Meridian Budget Briefing (EVT-000146, Approved, coordinator Daniel Tan) | Users: Priya Raj (Event Coordinator, not assigned), Marcus Wong (Venue Staff), Grace Lim (Event Operations Manager) | Expected attendance typed before each Search: 9999 (no venue is that large, so the search visibly returns nothing)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="327.75" customHeight="1" s="25">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM54 Meridian Budget Briefing (EVT-000146, Approved, coordinator Daniel Tan) | Users: Priya Raj (Event Coordinator, not assigned), Marcus Wong (Venue Staff), Grace Lim (Event Operations Manager) | Expected attendance typed before each Search: 9999 (no venue is that large, so the search visibly returns nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 2: The event page shows the 'Approved' status badge.
  Step 3: The message 'Only the assigned Coordinator can request a venue booking.' is shown above the venue list, and no venue has a 'Request booking' button.
@@ -2424,45 +2442,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="15.75" customHeight="1" s="25">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="25">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="25">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 2: The event page shows the 'Approved' status badge.
  Step 3: The message 'Only the assigned Coordinator can request a venue booking.' is shown above the venue list, and no venue has a 'Request booking' button.
@@ -2479,69 +2497,69 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="25">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="25">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="25">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B16" s="22" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
     <row r="17" ht="15.75" customHeight="1" s="25"/>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="25"/>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="25">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Step 2: The event page shows the 'Approved' status badge.
  Step 3: The message 'Only the assigned Coordinator can request a venue booking.' is shown above the venue list, and no venue has a 'Request booking' button.
@@ -2558,53 +2576,52 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="25">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="25">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="25">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B24" s="22" t="n">
         <v>46298</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
     <row r="27" ht="15.75" customHeight="1" s="25"/>
@@ -3582,6 +3599,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
   </hyperlinks>
@@ -3618,7 +3638,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC09</t>
         </is>
@@ -3630,7 +3650,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM54 Meridian Budget Briefing' (Approved, expects 20, layout Boardroom).
@@ -3645,7 +3665,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Meridian Budget Briefing'
 2. Click the 'Venue' tab
@@ -3666,7 +3686,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Meridian Budget Briefing (EVT-000146, Approved) | User: Daniel Tan (assigned coordinator) | Venue: Marina Boardroom 1 (MAR-BR1)</t>
         </is>
@@ -3678,7 +3698,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 2: 'Marina Boardroom 1 (MAR-BR1)' is marked 'Suitable' and has a 'Request booking' button.
@@ -3698,7 +3718,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3730,7 +3750,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 2: 'Marina Boardroom 1 (MAR-BR1)' is marked 'Suitable' and has a 'Request booking' button.
@@ -3806,7 +3826,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 2: 'Marina Boardroom 1 (MAR-BR1)' is marked 'Suitable' and has a 'Request booking' button.
@@ -4877,7 +4897,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC10</t>
         </is>
@@ -4889,7 +4909,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM54 Meridian Budget Briefing' (Approved, 5 Aug 2027 14:00–17:00, expects 20, layout Boardroom, no booking requests or equipment).
@@ -4904,7 +4924,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Meridian Budget Briefing'
 2. Click the 'Venue' tab
@@ -4931,7 +4951,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Meridian Budget Briefing (EVT-000146, Approved) | User: Daniel Tan (assigned coordinator) | Venue: Marina Boardroom 1 (MAR-BR1) | Equipment: Handheld Wireless Mic, Quantity 1</t>
         </is>
@@ -4943,7 +4963,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 4: A dialog 'Begin planning?' reads 'This is the first venue or equipment action for this event, so it will move from Approved to Planning. The organiser and ConnectSphere staff will see this status. This cannot be undone.' with 'Cancel' and 'Continue' buttons.
@@ -4965,7 +4985,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -4997,7 +5017,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 4: A dialog 'Begin planning?' reads 'This is the first venue or equipment action for this event, so it will move from Approved to Planning. The organiser and ConnectSphere staff will see this status. This cannot be undone.' with 'Cancel' and 'Continue' buttons.
@@ -5075,7 +5095,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000146 with the 'Approved' status badge.
 Step 4: A dialog 'Begin planning?' reads 'This is the first venue or equipment action for this event, so it will move from Approved to Planning. The organiser and ConnectSphere staff will see this status. This cannot be undone.' with 'Cancel' and 'Continue' buttons.
@@ -6148,7 +6168,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC11</t>
         </is>
@@ -6227,7 +6247,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7402,7 +7422,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC12</t>
         </is>
@@ -7414,7 +7434,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM54 Harbourline Agents Seminar' (Under review, expects 60, layout Theatre).</t>
@@ -7427,7 +7447,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Harbourline Agents Seminar'
 2. Click the 'Venue' tab
@@ -7442,7 +7462,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Harbourline Agents Seminar (EVT-000147, Under review) | User: Daniel Tan (assigned coordinator)</t>
         </is>
@@ -7454,7 +7474,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000147 with the 'Under review' status badge.
 Step 2: The 'Find a venue' page lists the venues checked for this event. The message 'A venue can be requested once this request has been approved.' is shown above the venue list, and no venue has a 'Request booking' button, including those marked 'Suitable'.
@@ -7469,7 +7489,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7501,7 +7521,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000147 with the 'Under review' status badge.
 Step 2: The 'Find a venue' page lists the venues checked for this event. The message 'A venue can be requested once this request has been approved.' is shown above the venue list, and no venue has a 'Request booking' button, including those marked 'Suitable'.
@@ -7572,7 +7592,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000147 with the 'Under review' status badge.
 Step 2: The 'Find a venue' page lists the venues checked for this event. The message 'A venue can be requested once this request has been approved.' is shown above the venue list, and no venue has a 'Request booking' button, including those marked 'Suitable'.
@@ -8638,7 +8658,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC13</t>
         </is>
@@ -8716,7 +8736,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -9898,7 +9918,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC14</t>
         </is>
@@ -9910,7 +9930,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Before: run `npm run fixtures:spm54` so 'SPM54 Kirana Store Managers Workshop' has no booking requests or equipment.
@@ -9926,7 +9946,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Kirana Store Managers Workshop'
 2. Click the 'Venue' tab
@@ -9948,7 +9968,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Kirana Store Managers Workshop (EVT-000150, Planning) | Venue: Orchard Seminar Room (ORC-SEM) | Date: 18 Aug 2027 | Slot: AM (07:00–12:00) | Equipment: Handheld Wireless Mic | Quantity: 2 | Technical requirements: Two roaming mics for the group discussions.</t>
         </is>
@@ -9960,7 +9980,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000150 with the 'Planning' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -9979,7 +9999,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10011,7 +10031,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000150 with the 'Planning' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -10086,7 +10106,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000150 with the 'Planning' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -11146,54 +11166,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="152.25" customHeight="1" s="25">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Wording chosen while building, to confirm: the 'Begin planning?' dialog text (TC01, TC04 to TC07); the search page's failure text now ends 'try searching again.'; the alert bodies 'This event has moved from Approved to Planning now that a venue booking has been requested.' and '…now that its equipment requirements are being worked on.' (TC04 to TC07), the Under review messages 'A venue can be requested once this request has been approved.' and 'Equipment can be recorded once this request has been approved.' (TC12), and the organiser Dashboard's four descriptions ('Requests you have started but not submitted yet.', 'Requests a coordinator is reviewing.', 'Approved requests waiting for planning to begin.', 'Events your coordinator is now planning.')</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
+      <c r="C2" s="29" t="n"/>
     </row>
     <row r="3" ht="44.25" customHeight="1" s="25">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-40-TC15 expects the move to Planning as soon as Find a venue opens. It now needs a 'Click Search' step before the 'Planning has started' message - its owner should update it.</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n"/>
+      <c r="C3" s="29" t="n"/>
     </row>
     <row r="4" ht="111.75" customHeight="1" s="25">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Other stories to re-run after this change: SPM-42-TC08 and TC09 request bookings for 'SPM42 Three-Session Forum' while it is Approved, which now moves it to Planning (their expected results do not mention the event's status). Any case in another story that requests a booking or changes equipment on an Under review event is now blocked. SPM-21 and SPM-30 quote the coordinator Dashboard's 'Awaiting your review' list: it now holds only Under review events (Approved and Planning have their own sections) and at most five, most recently updated first.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="29" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25"/>
     <row r="22" ht="15.75" customHeight="1" s="25"/>
@@ -12209,7 +12229,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC01</t>
         </is>
@@ -12221,7 +12241,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Before: run `npm run fixtures:spm54` so 'SPM54 Straits Clinical Forum' is back to Approved.
@@ -12236,7 +12256,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Straits Clinical Forum'
 2. Click the 'Venue' tab
@@ -12254,7 +12274,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Straits Clinical Forum (EVT-000145) | Starting status: Approved | Coordinator: Daniel Tan | Organiser: Evelyn Chen</t>
         </is>
@@ -12266,7 +12286,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000145 with the 'Approved' status badge, and 'Approved' next to Status in the Details card.
 Step 3: The 'Find a venue' search page opens with the subtitle 'Filled in from SPM54 Straits Clinical Forum's requirements. Change any filter and search again.' No 'Planning has started' alert is shown.
@@ -12283,7 +12303,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12315,7 +12335,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000145 with the 'Approved' status badge, and 'Approved' next to Status in the Details card.
 Step 3: The 'Find a venue' search page opens with the subtitle 'Filled in from SPM54 Straits Clinical Forum's requirements. Change any filter and search again.' No 'Planning has started' alert is shown.
@@ -12356,7 +12376,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12388,7 +12408,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000145 with the 'Approved' status badge, and 'Approved' next to Status in the Details card.
 Step 3: The 'Find a venue' search page opens with the subtitle 'Filled in from SPM54 Straits Clinical Forum's requirements. Change any filter and search again.' No 'Planning has started' alert is shown.
@@ -12429,7 +12449,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13456,7 +13476,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC02</t>
         </is>
@@ -13468,7 +13488,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC01 has just been run ('SPM54 Straits Clinical Forum' moved to Planning by Daniel Tan).
 Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), Event Organiser of 'SPM54 Straits Clinical Forum'.
@@ -13482,7 +13502,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'Dashboard' in the sidebar
 2. Click 'My Events' in the sidebar
@@ -13497,7 +13517,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Straits Clinical Forum (EVT-000145) | Organiser: Evelyn Chen | Coordinator: Daniel Tan</t>
         </is>
@@ -13509,7 +13529,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: Under the 'Planning' heading on the Dashboard, 'SPM54 Straits Clinical Forum' is listed with the 'Planning' status badge. It is the first event in that section (each section shows the five most recently updated) and is not under 'Approved'.
 Step 2: Under 'Submitted', 'SPM54 Straits Clinical Forum' is listed with 'Planning' in the Status column.
@@ -13524,7 +13544,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13556,7 +13576,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: Under the 'Planning' heading on the Dashboard, 'SPM54 Straits Clinical Forum' is listed with the 'Planning' status badge. It is the first event in that section (each section shows the five most recently updated) and is not under 'Approved'.
 Step 2: Under 'Submitted', 'SPM54 Straits Clinical Forum' is listed with 'Planning' in the Status column.
@@ -13595,7 +13615,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14630,7 +14650,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC03</t>
         </is>
@@ -14642,7 +14662,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser of 'SPM54 Meridian Budget Briefing' (Approved, coordinator Daniel Tan). No test case moves this event to Planning.
@@ -14656,7 +14676,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'Dashboard' in the sidebar
 2. Click 'My Events' in the sidebar
@@ -14672,7 +14692,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Meridian Budget Briefing (EVT-000146) | Status: Approved | Organiser: James Koh</t>
         </is>
@@ -14684,7 +14704,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: Under the 'Approved' heading on the Dashboard, 'SPM54 Meridian Budget Briefing' is listed with the 'Approved' status badge. It is not under 'Planning'.
 Step 2: Under 'Submitted', 'SPM54 Meridian Budget Briefing' is listed with 'Approved' in the Status column.
@@ -14700,7 +14720,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14732,7 +14752,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: Under the 'Approved' heading on the Dashboard, 'SPM54 Meridian Budget Briefing' is listed with the 'Approved' status badge. It is not under 'Planning'.
 Step 2: Under 'Submitted', 'SPM54 Meridian Budget Briefing' is listed with 'Approved' in the Status column.
@@ -14804,7 +14824,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: Under the 'Approved' heading on the Dashboard, 'SPM54 Meridian Budget Briefing' is listed with the 'Approved' status badge. It is not under 'Planning'.
 Step 2: Under 'Submitted', 'SPM54 Meridian Budget Briefing' is listed with 'Approved' in the Status column.
@@ -15878,7 +15898,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC04</t>
         </is>
@@ -15890,7 +15910,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Before: run `npm run fixtures:spm54` so 'SPM54 Pearl Delta Supplier Briefing' is back to Approved with no booking requests.
@@ -15907,7 +15927,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Pearl Delta Supplier Briefing'
 2. Click the 'Venue' tab
@@ -15925,7 +15945,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Pearl Delta Supplier Briefing (EVT-000151) | Starting status: Approved | Venue: Orchard Seminar Room (ORC-SEM) | Date: 25 Aug 2027 | Slot: AM (07:00–12:00)</t>
         </is>
@@ -15937,7 +15957,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000151 with the 'Approved' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -15955,7 +15975,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -15987,7 +16007,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000151 with the 'Approved' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -16061,7 +16081,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000151 with the 'Approved' status badge.
 Step 2: 'Orchard Seminar Room (ORC-SEM)' is marked 'Suitable' and has a 'Request booking' button.
@@ -17132,7 +17152,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC05</t>
         </is>
@@ -17144,7 +17164,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
 Before: run `npm run fixtures:spm54` so 'SPM54 Sundara Service Workshop' is back to Approved with no equipment.
@@ -17159,7 +17179,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Sundara Service Workshop'
 2. Click the 'Equipment' tab
@@ -17177,7 +17197,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM54 Sundara Service Workshop (EVT-000152) | Starting status: Approved | Equipment: Handheld Wireless Mic | Quantity: 2</t>
         </is>
@@ -17189,7 +17209,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000152 with the 'Approved' status badge.
 Step 2: The 'Equipment requirements' page shows EVT-000152 with the 'Approved' status badge, 'Nothing requested yet' and the 'Add equipment' form.
@@ -17205,7 +17225,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17237,7 +17257,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000152 with the 'Approved' status badge.
 Step 2: The 'Equipment requirements' page shows EVT-000152 with the 'Approved' status badge, 'Nothing requested yet' and the 'Add equipment' form.
@@ -17309,7 +17329,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000152 with the 'Approved' status badge.
 Step 2: The 'Equipment requirements' page shows EVT-000152 with the 'Approved' status badge, 'Nothing requested yet' and the 'Add equipment' form.
@@ -18376,7 +18396,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC06</t>
         </is>
@@ -18449,7 +18469,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18481,7 +18501,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000153 with the 'Approved' status badge.
 Step 2: The 'Equipment requirements' page shows EVT-000153 with the 'Approved' status badge. The 'Requested items' card shows '1 item': 'Handheld Wireless Mic' with a 'Requested' badge and Quantity 2.
@@ -18554,7 +18574,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 1: The event page shows EVT-000153 with the 'Approved' status badge.
 Step 2: The 'Equipment requirements' page shows EVT-000153 with the 'Approved' status badge. The 'Requested items' card shows '1 item': 'Handheld Wireless Mic' with a 'Requested' badge and Quantity 2.
@@ -19622,7 +19642,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC07</t>
         </is>
@@ -19693,7 +19713,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>

--- a/docs/test-cases/SPM-54_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-54_Test_Cases.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -70,6 +70,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -166,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -237,6 +241,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1101,11 +1108,15 @@
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>#103</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1150,8 +1161,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
@@ -8636,7 +8645,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -8644,46 +8653,53 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="64" customHeight="1" s="25">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-23): Step 8 now reads 'A venue cannot be requested for a completed, cancelled, rejected or withdrawn event.' instead of 'A venue cannot be requested for a completed, cancelled or rejected event.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="25">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="25">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-54-TC13</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="125.25" customHeight="1" s="25">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4" ht="125.25" customHeight="1" s="25">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
  Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM54 Anchorpoint Fleet Briefing' (Confirmed) and 'SPM54 Nusantara Overnight Sprint' (Rejected, reason 'No ConnectSphere venue is licensed for overnight occupancy.').</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="192.75" customHeight="1" s="25">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5" ht="192.75" customHeight="1" s="25">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Anchorpoint Fleet Briefing'
  2. Click the 'Venue' tab
@@ -8700,25 +8716,25 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" s="25">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Events: SPM54 Anchorpoint Fleet Briefing (EVT-000148, Confirmed), SPM54 Nusantara Overnight Sprint (EVT-000149, Rejected) | User: Daniel Tan (assigned coordinator of both) | Expected attendance typed before each Search: 9999 (no venue is that large, so the search visibly returns nothing)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="192.75" customHeight="1" s="25">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7" ht="192.75" customHeight="1" s="25">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8730,45 +8746,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="25">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="25">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="15.75" customHeight="1" s="25">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="25">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="25">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8780,69 +8796,69 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="25">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="25">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="25">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B16" s="22" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
     <row r="17" ht="15.75" customHeight="1" s="25"/>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="25"/>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="25">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8854,53 +8870,52 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="25">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="25">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="25">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B24" s="22" t="n">
         <v>46298</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
     <row r="27" ht="15.75" customHeight="1" s="25"/>
@@ -9878,6 +9893,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/docs/test-cases/SPM-54_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-54_Test_Cases.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -70,10 +70,6 @@
     </font>
     <font>
       <color rgb="FF000000"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -170,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -241,9 +237,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1108,15 +1101,11 @@
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="inlineStr">
-        <is>
-          <t>#103</t>
-        </is>
-      </c>
+      <c r="I16" s="29" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1161,6 +1150,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
@@ -8645,7 +8636,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -8653,53 +8644,46 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64" customHeight="1" s="25">
-      <c r="A1" s="32" t="inlineStr">
-        <is>
-          <t>v2 (2026-10-23): Step 8 now reads 'A venue cannot be requested for a completed, cancelled, rejected or withdrawn event.' instead of 'A venue cannot be requested for a completed, cancelled or rejected event.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="25">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="25">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="25">
+      <c r="B1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>SPM-54-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.25" customHeight="1" s="25">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>SPM-54-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="125.25" customHeight="1" s="25">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm54` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM54 …' events, EVT-000145 to EVT-000154, never anyone else's data).
  Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM54 Anchorpoint Fleet Briefing' (Confirmed) and 'SPM54 Nusantara Overnight Sprint' (Rejected, reason 'No ConnectSphere venue is licensed for overnight occupancy.').</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="192.75" customHeight="1" s="25">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="4" ht="192.75" customHeight="1" s="25">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM54 Anchorpoint Fleet Briefing'
  2. Click the 'Venue' tab
@@ -8716,25 +8700,25 @@
         </is>
       </c>
     </row>
-    <row r="6" s="25">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Events: SPM54 Anchorpoint Fleet Briefing (EVT-000148, Confirmed), SPM54 Nusantara Overnight Sprint (EVT-000149, Rejected) | User: Daniel Tan (assigned coordinator of both) | Expected attendance typed before each Search: 9999 (no venue is that large, so the search visibly returns nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="192.75" customHeight="1" s="25">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Events: SPM54 Anchorpoint Fleet Briefing (EVT-000148, Confirmed), SPM54 Nusantara Overnight Sprint (EVT-000149, Rejected) | User: Daniel Tan (assigned coordinator of both) | Expected attendance typed before each Search: 9999 (no venue is that large, so the search visibly returns nothing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="192.75" customHeight="1" s="25">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8746,45 +8730,45 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="25">
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="25">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B8" s="17" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="9" ht="15.75" customHeight="1" s="25"/>
+    <row r="10" ht="15.75" customHeight="1" s="25">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="n"/>
+    </row>
     <row r="11" ht="15.75" customHeight="1" s="25">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="25">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8796,69 +8780,69 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="15.75" customHeight="1" s="25">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="15.75" customHeight="1" s="25">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="25">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="25">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B15" s="22" t="n">
         <v>46296</v>
       </c>
     </row>
+    <row r="16" ht="15.75" customHeight="1" s="25"/>
     <row r="17" ht="15.75" customHeight="1" s="25"/>
-    <row r="18" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n"/>
+    </row>
     <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="25">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Confirmed' status badge.
  Step 5: The venue list is replaced by 'No venues match these filters'. No 'Begin planning?' dialog and no 'Planning has started' alert is shown.
@@ -8870,52 +8854,53 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="15.75" customHeight="1" s="25">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Janelle</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="25">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="25">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B23" s="22" t="n">
         <v>46298</v>
       </c>
     </row>
+    <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
     <row r="27" ht="15.75" customHeight="1" s="25"/>
@@ -9893,9 +9878,6 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
